--- a/result/Table202510.xlsx
+++ b/result/Table202510.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I12" t="n">
         <v>3.95</v>
       </c>
       <c r="J12" t="n">
-        <v>3.28</v>
+        <v>3.33</v>
       </c>
       <c r="K12" t="n">
-        <v>-16.96</v>
+        <v>-15.7</v>
       </c>
       <c r="L12" t="n">
-        <v>-16962.03</v>
+        <v>-15696.2</v>
       </c>
     </row>
     <row r="13">

--- a/result/Table202510.xlsx
+++ b/result/Table202510.xlsx
@@ -516,24 +516,24 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="I2" t="n">
         <v>5.53</v>
       </c>
       <c r="J2" t="n">
-        <v>5.25</v>
+        <v>6.1</v>
       </c>
       <c r="K2" t="n">
-        <v>-5.06</v>
+        <v>10.31</v>
       </c>
       <c r="L2" t="n">
-        <v>-5063.29</v>
+        <v>10307.41</v>
       </c>
     </row>
     <row r="3">
@@ -812,24 +812,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
         <v>36.94</v>
       </c>
       <c r="J8" t="n">
-        <v>42.49</v>
+        <v>41.17</v>
       </c>
       <c r="K8" t="n">
-        <v>15.02</v>
+        <v>11.45</v>
       </c>
       <c r="L8" t="n">
-        <v>15024.36</v>
+        <v>11451</v>
       </c>
     </row>
     <row r="9">
@@ -858,24 +858,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
         <v>605.16</v>
       </c>
       <c r="J9" t="n">
-        <v>560.08</v>
+        <v>520</v>
       </c>
       <c r="K9" t="n">
-        <v>-7.45</v>
+        <v>-14.07</v>
       </c>
       <c r="L9" t="n">
-        <v>-7449.27</v>
+        <v>-14072.31</v>
       </c>
     </row>
     <row r="10">
@@ -1204,24 +1204,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="I16" t="n">
         <v>12.72</v>
       </c>
       <c r="J16" t="n">
-        <v>11.66</v>
+        <v>12.25</v>
       </c>
       <c r="K16" t="n">
-        <v>-8.33</v>
+        <v>-3.69</v>
       </c>
       <c r="L16" t="n">
-        <v>-8333.33</v>
+        <v>-3694.97</v>
       </c>
     </row>
     <row r="17">
@@ -1400,24 +1400,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="I20" t="n">
         <v>14.03</v>
       </c>
       <c r="J20" t="n">
-        <v>13.73</v>
+        <v>13</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.14</v>
+        <v>-7.34</v>
       </c>
       <c r="L20" t="n">
-        <v>-2138.28</v>
+        <v>-7341.41</v>
       </c>
     </row>
     <row r="21">
@@ -1542,24 +1542,24 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I23" t="n">
         <v>4.08</v>
       </c>
       <c r="J23" t="n">
-        <v>3.74</v>
+        <v>8.49</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.33</v>
+        <v>108.09</v>
       </c>
       <c r="L23" t="n">
-        <v>-8333.33</v>
+        <v>108088.24</v>
       </c>
     </row>
     <row r="24">
@@ -1738,24 +1738,24 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
         <v>6.85</v>
       </c>
       <c r="J27" t="n">
-        <v>6.32</v>
+        <v>6.02</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.74</v>
+        <v>-12.12</v>
       </c>
       <c r="L27" t="n">
-        <v>-7737.23</v>
+        <v>-12116.79</v>
       </c>
     </row>
     <row r="28">
@@ -1834,24 +1834,24 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
         <v>28.92</v>
       </c>
       <c r="J29" t="n">
-        <v>26.6</v>
+        <v>25.97</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.02</v>
+        <v>-10.2</v>
       </c>
       <c r="L29" t="n">
-        <v>-8022.13</v>
+        <v>-10200.55</v>
       </c>
     </row>
     <row r="30">
@@ -2122,24 +2122,24 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I35" t="n">
         <v>14</v>
       </c>
       <c r="J35" t="n">
-        <v>13.74</v>
+        <v>12.98</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.86</v>
+        <v>-7.29</v>
       </c>
       <c r="L35" t="n">
-        <v>-1857.14</v>
+        <v>-7285.71</v>
       </c>
     </row>
     <row r="36">
@@ -2214,24 +2214,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="I37" t="n">
         <v>22.52</v>
       </c>
       <c r="J37" t="n">
-        <v>25.59</v>
+        <v>29.99</v>
       </c>
       <c r="K37" t="n">
-        <v>13.63</v>
+        <v>33.17</v>
       </c>
       <c r="L37" t="n">
-        <v>13632.33</v>
+        <v>33170.52</v>
       </c>
     </row>
     <row r="38">
@@ -2360,24 +2360,24 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I40" t="n">
         <v>13.18</v>
       </c>
       <c r="J40" t="n">
-        <v>12.25</v>
+        <v>11.65</v>
       </c>
       <c r="K40" t="n">
-        <v>-7.06</v>
+        <v>-11.61</v>
       </c>
       <c r="L40" t="n">
-        <v>-7056.15</v>
+        <v>-11608.5</v>
       </c>
     </row>
     <row r="41">
@@ -2506,24 +2506,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I43" t="n">
         <v>13</v>
       </c>
       <c r="J43" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="K43" t="n">
-        <v>-9.23</v>
+        <v>6.92</v>
       </c>
       <c r="L43" t="n">
-        <v>-9230.77</v>
+        <v>6923.08</v>
       </c>
     </row>
     <row r="44">
@@ -3094,24 +3094,24 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I55" t="n">
         <v>46.4</v>
       </c>
       <c r="J55" t="n">
-        <v>44.46</v>
+        <v>40.5</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.18</v>
+        <v>-12.72</v>
       </c>
       <c r="L55" t="n">
-        <v>-4181.03</v>
+        <v>-12715.52</v>
       </c>
     </row>
     <row r="56">
@@ -3190,24 +3190,24 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I57" t="n">
         <v>11.29</v>
       </c>
       <c r="J57" t="n">
-        <v>10.48</v>
+        <v>10.17</v>
       </c>
       <c r="K57" t="n">
-        <v>-7.17</v>
+        <v>-9.92</v>
       </c>
       <c r="L57" t="n">
-        <v>-7174.49</v>
+        <v>-9920.280000000001</v>
       </c>
     </row>
     <row r="58">
@@ -3236,24 +3236,24 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I58" t="n">
         <v>96.31</v>
       </c>
       <c r="J58" t="n">
-        <v>90</v>
+        <v>84.86</v>
       </c>
       <c r="K58" t="n">
-        <v>-6.55</v>
+        <v>-11.89</v>
       </c>
       <c r="L58" t="n">
-        <v>-6551.76</v>
+        <v>-11888.69</v>
       </c>
     </row>
     <row r="59">
@@ -3282,24 +3282,24 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I59" t="n">
         <v>100.96</v>
       </c>
       <c r="J59" t="n">
-        <v>104.66</v>
+        <v>130.79</v>
       </c>
       <c r="K59" t="n">
-        <v>3.66</v>
+        <v>29.55</v>
       </c>
       <c r="L59" t="n">
-        <v>3664.82</v>
+        <v>29546.35</v>
       </c>
     </row>
     <row r="60">

--- a/result/Table202510.xlsx
+++ b/result/Table202510.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I12" t="n">
         <v>3.95</v>
       </c>
       <c r="J12" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="K12" t="n">
-        <v>-15.7</v>
+        <v>-17.22</v>
       </c>
       <c r="L12" t="n">
-        <v>-15696.2</v>
+        <v>-17215.19</v>
       </c>
     </row>
     <row r="13">

--- a/result/Table202510.xlsx
+++ b/result/Table202510.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I12" t="n">
         <v>3.95</v>
       </c>
       <c r="J12" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="K12" t="n">
-        <v>-17.22</v>
+        <v>-19.75</v>
       </c>
       <c r="L12" t="n">
-        <v>-17215.19</v>
+        <v>-19746.84</v>
       </c>
     </row>
     <row r="13">

--- a/result/Table202510.xlsx
+++ b/result/Table202510.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1013,19 +1013,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I12" t="n">
         <v>3.95</v>
       </c>
       <c r="J12" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="K12" t="n">
-        <v>-19.75</v>
+        <v>-20.76</v>
       </c>
       <c r="L12" t="n">
-        <v>-19746.84</v>
+        <v>-20759.49</v>
       </c>
     </row>
     <row r="13">
